--- a/outputs/qc/qc_missing_rate.xlsx
+++ b/outputs/qc/qc_missing_rate.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,7 +471,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Mn</t>
+          <t>altitude</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -481,7 +481,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>geology</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -491,7 +491,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>Mn</t>
         </is>
       </c>
       <c r="B8" t="n">
@@ -501,7 +501,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>K</t>
+          <t>N</t>
         </is>
       </c>
       <c r="B9" t="n">
@@ -511,7 +511,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SOM</t>
+          <t>P</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -521,7 +521,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CEC</t>
+          <t>K</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -531,7 +531,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>water content</t>
+          <t>SOM</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -541,7 +541,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Particle content</t>
+          <t>CEC</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -551,7 +551,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>clay content</t>
+          <t>water content</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -561,7 +561,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>sand content</t>
+          <t>Particle content</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -571,7 +571,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>soil type</t>
+          <t>clay content</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -581,7 +581,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>bulk density</t>
+          <t>sand content</t>
         </is>
       </c>
       <c r="B17" t="n">
@@ -591,7 +591,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Vegetation cover type</t>
+          <t>Land use type</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -601,7 +601,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Distance from pollution source</t>
+          <t>soil type</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -611,7 +611,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>source_sheet</t>
+          <t>bulk density</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -621,7 +621,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>crop</t>
+          <t>Vegetation cover type</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -631,7 +631,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ph_bin_from_sheet</t>
+          <t>Distance from pollution source</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -641,10 +641,40 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>source_sheet</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>crop</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ph_bin_from_sheet</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>ph_bin</t>
         </is>
       </c>
-      <c r="B23" t="n">
+      <c r="B26" t="n">
         <v>0</v>
       </c>
     </row>
